--- a/artfynd/A 19512-2022 artfynd.xlsx
+++ b/artfynd/A 19512-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 19512-2022 artfynd.xlsx
+++ b/artfynd/A 19512-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -824,6 +824,118 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131354120</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Morkullsåsmossen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>483775</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6672440</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19512-2022 artfynd.xlsx
+++ b/artfynd/A 19512-2022 artfynd.xlsx
@@ -830,7 +830,7 @@
         <v>131354120</v>
       </c>
       <c r="B3" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19512-2022 artfynd.xlsx
+++ b/artfynd/A 19512-2022 artfynd.xlsx
@@ -830,7 +830,7 @@
         <v>131354120</v>
       </c>
       <c r="B3" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19512-2022 artfynd.xlsx
+++ b/artfynd/A 19512-2022 artfynd.xlsx
@@ -830,7 +830,7 @@
         <v>131354120</v>
       </c>
       <c r="B3" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19512-2022 artfynd.xlsx
+++ b/artfynd/A 19512-2022 artfynd.xlsx
@@ -830,7 +830,7 @@
         <v>131354120</v>
       </c>
       <c r="B3" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19512-2022 artfynd.xlsx
+++ b/artfynd/A 19512-2022 artfynd.xlsx
@@ -830,7 +830,7 @@
         <v>131354120</v>
       </c>
       <c r="B3" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19512-2022 artfynd.xlsx
+++ b/artfynd/A 19512-2022 artfynd.xlsx
@@ -830,7 +830,7 @@
         <v>131354120</v>
       </c>
       <c r="B3" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19512-2022 artfynd.xlsx
+++ b/artfynd/A 19512-2022 artfynd.xlsx
@@ -830,7 +830,7 @@
         <v>131354120</v>
       </c>
       <c r="B3" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19512-2022 artfynd.xlsx
+++ b/artfynd/A 19512-2022 artfynd.xlsx
@@ -830,7 +830,7 @@
         <v>131354120</v>
       </c>
       <c r="B3" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19512-2022 artfynd.xlsx
+++ b/artfynd/A 19512-2022 artfynd.xlsx
@@ -830,7 +830,7 @@
         <v>131354120</v>
       </c>
       <c r="B3" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19512-2022 artfynd.xlsx
+++ b/artfynd/A 19512-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>7254933</v>
       </c>
       <c r="B2" t="n">
-        <v>77532</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -725,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483708.637613057</v>
+        <v>483709</v>
       </c>
       <c r="R2" t="n">
-        <v>6672469.174028373</v>
+        <v>6672469</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -758,19 +753,9 @@
           <t>2014-04-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-04-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -830,7 +815,7 @@
         <v>131354120</v>
       </c>
       <c r="B3" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
